--- a/marketing_report/outputs/Cursos/Analisis_UTM/analisis_utm_completo.xlsx
+++ b/marketing_report/outputs/Cursos/Analisis_UTM/analisis_utm_completo.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -501,7 +501,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -514,18 +514,84 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>chatgpt.com</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>marketing_cloud</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -540,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,16 +648,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -600,7 +666,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>carreras</t>
+          <t>14876203835</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -613,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -622,20 +688,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23084310717</t>
+          <t>carreras</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
@@ -644,20 +710,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14876203835</t>
+          <t>23084310717</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -666,20 +732,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>8419948319</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
         <v>100</v>
@@ -688,20 +754,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14909096324</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>100</v>
@@ -710,20 +776,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23277494379</t>
+          <t>14875022827</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>100</v>
@@ -732,22 +798,154 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8419948319</t>
+          <t>14909096324</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>120235998797960048</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>14896121927</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>14909223761</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15357460006</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20612364611</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>23277494379</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
         <v>100</v>
       </c>
     </row>
@@ -762,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,16 +1002,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -835,7 +1033,7 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -848,16 +1046,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
@@ -882,6 +1080,50 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -928,13 +1170,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -944,13 +1186,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -960,13 +1202,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/marketing_report/outputs/Cursos/Analisis_UTM/analisis_utm_completo.xlsx
+++ b/marketing_report/outputs/Cursos/Analisis_UTM/analisis_utm_completo.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -510,88 +510,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>ig</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chatgpt.com</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ig</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>marketing_cloud</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -606,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,20 +578,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21676468921</t>
+          <t>120235998797960048</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -670,16 +604,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -688,20 +622,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>carreras</t>
+          <t>21676468921</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
@@ -710,242 +644,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23084310717</t>
+          <t>carreras</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>8419948319</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>organic</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>14875022827</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>14909096324</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>120235998797960048</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>14896121927</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>14909223761</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>15357460006</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20612364611</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>23277494379</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
         <v>100</v>
       </c>
     </row>
@@ -960,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,16 +716,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -1020,20 +734,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>leadads</t>
+          <t>alcance</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -1042,88 +756,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feed</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>alcance</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1170,13 +818,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1186,13 +834,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1202,13 +850,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
